--- a/SCIE용/excel/29_stage_classifier_eval.xlsx
+++ b/SCIE용/excel/29_stage_classifier_eval.xlsx
@@ -236,7 +236,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>0.0501</t>
+          <t>0.0502</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0.0619</t>
+          <t>0.0620</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="H20" s="0" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0.0380</t>
+          <t>0.0381</t>
         </is>
       </c>
       <c r="H24" s="0" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0.0562</t>
+          <t>0.0563</t>
         </is>
       </c>
       <c r="H25" s="0" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0.1250</t>
+          <t>0.1249</t>
         </is>
       </c>
       <c r="H27" s="0" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="H28" s="0" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0.0169</t>
+          <t>0.0170</t>
         </is>
       </c>
       <c r="H30" s="0" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="H32" s="0" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0.0129</t>
+          <t>0.0130</t>
         </is>
       </c>
       <c r="H36" s="0" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0.0528</t>
+          <t>0.0529</t>
         </is>
       </c>
       <c r="H37" s="0" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1409</t>
         </is>
       </c>
       <c r="H38" s="0" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0.0027</t>
+          <t>0.0028</t>
         </is>
       </c>
       <c r="H46" s="0" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0.0092</t>
+          <t>0.0093</t>
         </is>
       </c>
       <c r="H53" s="0" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0.1485</t>
+          <t>0.1484</t>
         </is>
       </c>
       <c r="H58" s="0" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0.0254</t>
+          <t>0.0255</t>
         </is>
       </c>
       <c r="H62" s="0" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0.1788</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="H70" s="0" t="inlineStr">
